--- a/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
+++ b/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S2.xlsx
@@ -16617,7 +16617,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16697,7 +16697,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16777,10 +16777,11 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="20">
       <c r="A16" s="23" t="inlineStr">
         <is>
